--- a/frontend/destination/Estructura transferencia transito.xlsx
+++ b/frontend/destination/Estructura transferencia transito.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.3\Logistica\SIESA\Luis Viana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD4F8A7-D3CC-45B9-BF39-58416AE31763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B0465D-EA2D-42AD-8D9C-5096C6B99F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B0DC4666-983E-479B-8CBB-09F03F47BF94}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="44">
   <si>
     <t>Centro de operación</t>
   </si>
@@ -80,34 +80,97 @@
     <t>Talla</t>
   </si>
   <si>
+    <t>Cajas</t>
+  </si>
+  <si>
     <t>002</t>
   </si>
   <si>
     <t xml:space="preserve">UND </t>
   </si>
   <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>20260415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210  </t>
+  </si>
+  <si>
+    <t>3TB</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>BLANCO</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
     <t>028</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>016</t>
-  </si>
-  <si>
-    <t>026</t>
-  </si>
-  <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>2TL</t>
-  </si>
-  <si>
-    <t>20260320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221  </t>
+    <t>030</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -491,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52CE5A08-B450-4D76-92CC-8C2D8892D02A}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.109375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -499,11 +562,11 @@
     <col min="3" max="3" width="28.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.109375" style="1"/>
-    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="12.21875" style="1" customWidth="1"/>
     <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.109375" style="1"/>
@@ -511,7 +574,7 @@
     <col min="15" max="16384" width="11.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -557,193 +620,1108 @@
       <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="1">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1">
+        <v>12</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="1">
+        <v>24</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="1">
+        <v>12</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="1">
+        <v>12</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="1">
+        <v>24</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="1">
+        <v>12</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="1">
+        <v>12</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="1">
+        <v>18</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="1">
+        <v>12</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="1">
-        <v>72</v>
-      </c>
-      <c r="L2" s="1">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1">
-        <v>340223</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="1">
+        <v>12</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="1">
-        <v>180</v>
-      </c>
-      <c r="L3" s="1">
-        <v>0</v>
-      </c>
-      <c r="M3" s="1">
-        <v>340223</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="1">
-        <v>72</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>340223</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="1">
+        <v>12</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="1">
+        <v>12</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="1">
+        <v>12</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="1">
+        <v>12</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="1">
+        <v>12</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="1">
+        <v>12</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="1">
+        <v>12</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="1">
-        <v>90</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
-        <v>340223</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>16</v>
+      <c r="F22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="1">
+        <v>24</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="1">
+        <v>12</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>303189</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
